--- a/data/trans_orig/IMC_inf_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Provincia-trans_orig.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -3507,25 +3507,25 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>62248</v>
+        <v>62898</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>53967</v>
+        <v>54671</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>70405</v>
+        <v>71306</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.5325873745210858</v>
+        <v>0.5381493813409921</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.4617309227311792</v>
+        <v>0.4677589899593957</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.6023783929151421</v>
+        <v>0.6100854741577099</v>
       </c>
       <c r="J43" s="5" t="n">
         <v>108</v>
@@ -3549,25 +3549,25 @@
         <v>0.7146423553995289</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="R43" s="5" t="n">
-        <v>136822</v>
+        <v>137472</v>
       </c>
       <c r="S43" s="5" t="n">
-        <v>124679</v>
+        <v>125279</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>149048</v>
+        <v>149818</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>0.5884571881380098</v>
+        <v>0.5912531169880537</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>0.5362290997777606</v>
+        <v>0.5388094962664947</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>0.6410378602052673</v>
+        <v>0.644350097281457</v>
       </c>
     </row>
     <row r="44">
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>7523</v>
+        <v>6873</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>4129</v>
+        <v>3496</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>12441</v>
+        <v>11684</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.06436892848335282</v>
+        <v>0.05880692166344658</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.0353280572951741</v>
+        <v>0.02991381638644037</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.1064429867707111</v>
+        <v>0.09996523047690037</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>9</v>
@@ -3620,25 +3620,25 @@
         <v>0.0946533693124558</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R44" s="5" t="n">
-        <v>13751</v>
+        <v>13101</v>
       </c>
       <c r="S44" s="5" t="n">
-        <v>8762</v>
+        <v>8300</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>20457</v>
+        <v>20022</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>0.05914197918830078</v>
+        <v>0.05634605033825695</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>0.0376863612211614</v>
+        <v>0.03569622519305601</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>0.08798464817673264</v>
+        <v>0.0861136240242926</v>
       </c>
     </row>
     <row r="45">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
@@ -4367,25 +4367,25 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>304213</v>
+        <v>304863</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>285570</v>
+        <v>286131</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>324293</v>
+        <v>324710</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.5024551392778183</v>
+        <v>0.5035288487457855</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.4716626792796453</v>
+        <v>0.4725897824735413</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.5356197657406884</v>
+        <v>0.5363088091232465</v>
       </c>
       <c r="J55" s="5" t="n">
         <v>525</v>
@@ -4409,25 +4409,25 @@
         <v>0.6454744660949693</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="R55" s="5" t="n">
-        <v>659528</v>
+        <v>660178</v>
       </c>
       <c r="S55" s="5" t="n">
-        <v>633140</v>
+        <v>633820</v>
       </c>
       <c r="T55" s="5" t="n">
-        <v>687943</v>
+        <v>688456</v>
       </c>
       <c r="U55" s="6" t="n">
-        <v>0.5572576635126306</v>
+        <v>0.5578069385938749</v>
       </c>
       <c r="V55" s="6" t="n">
-        <v>0.5349609214065915</v>
+        <v>0.5355359463257564</v>
       </c>
       <c r="W55" s="6" t="n">
-        <v>0.5812662489721956</v>
+        <v>0.5816993726167565</v>
       </c>
     </row>
     <row r="56">
@@ -4438,25 +4438,25 @@
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>26250</v>
+        <v>25599</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>19267</v>
+        <v>18573</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>34699</v>
+        <v>34180</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.04335525635786645</v>
+        <v>0.04228154688989916</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.03182265127449958</v>
+        <v>0.03067645825931641</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.05731068622694988</v>
+        <v>0.0564528716715501</v>
       </c>
       <c r="J56" s="5" t="n">
         <v>29</v>
@@ -4480,25 +4480,25 @@
         <v>0.0458607535520415</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R56" s="5" t="n">
-        <v>45282</v>
+        <v>44632</v>
       </c>
       <c r="S56" s="5" t="n">
-        <v>36104</v>
+        <v>35378</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>57176</v>
+        <v>56272</v>
       </c>
       <c r="U56" s="6" t="n">
-        <v>0.03826000231423884</v>
+        <v>0.03771072723299453</v>
       </c>
       <c r="V56" s="6" t="n">
-        <v>0.03050524197936881</v>
+        <v>0.02989174778838683</v>
       </c>
       <c r="W56" s="6" t="n">
-        <v>0.04830994509272634</v>
+        <v>0.04754635947722598</v>
       </c>
     </row>
     <row r="57">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
